--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.07278816391568</v>
+        <v>3.586828076636298</v>
       </c>
       <c r="D2" t="n">
-        <v>21.73975504608738</v>
+        <v>3.532710194989199</v>
       </c>
       <c r="E2" t="n">
-        <v>14.65595542726699</v>
+        <v>2.381592756930885</v>
       </c>
       <c r="F2" t="n">
-        <v>9.904048242526999</v>
+        <v>1.609407839410637</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.77182227203271</v>
+        <v>5.487921119205317</v>
       </c>
       <c r="D3" t="n">
-        <v>34.1249858883807</v>
+        <v>5.545310206861864</v>
       </c>
       <c r="E3" t="n">
-        <v>14.65595542726699</v>
+        <v>2.381592756930885</v>
       </c>
       <c r="F3" t="n">
-        <v>9.904048242526999</v>
+        <v>1.609407839410637</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.48926339315872</v>
+        <v>6.092005301388292</v>
       </c>
       <c r="D4" t="n">
-        <v>21.63447187750804</v>
+        <v>3.515601680095056</v>
       </c>
       <c r="E4" t="n">
-        <v>14.65595542726699</v>
+        <v>2.381592756930885</v>
       </c>
       <c r="F4" t="n">
-        <v>9.904048242526999</v>
+        <v>1.609407839410637</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.78724033299328</v>
+        <v>5.490426554111408</v>
       </c>
       <c r="D5" t="n">
-        <v>33.53230370120371</v>
+        <v>5.448999351445603</v>
       </c>
       <c r="E5" t="n">
-        <v>14.65595542726699</v>
+        <v>2.381592756930885</v>
       </c>
       <c r="F5" t="n">
-        <v>9.904048242526999</v>
+        <v>1.609407839410637</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.03224040274365</v>
+        <v>9.105239065445843</v>
       </c>
       <c r="D6" t="n">
-        <v>36.30356072848549</v>
+        <v>5.899328618378893</v>
       </c>
       <c r="E6" t="n">
-        <v>14.65595542726699</v>
+        <v>2.381592756930885</v>
       </c>
       <c r="F6" t="n">
-        <v>9.904048242526999</v>
+        <v>1.609407839410637</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.992918891152889</v>
+        <v>1.298849319812345</v>
       </c>
       <c r="D7" t="n">
-        <v>8.042166449230194</v>
+        <v>1.306852047999907</v>
       </c>
       <c r="E7" t="n">
-        <v>14.65595542726699</v>
+        <v>2.381592756930885</v>
       </c>
       <c r="F7" t="n">
-        <v>9.904048242526999</v>
+        <v>1.609407839410637</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
